--- a/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -149,6 +149,18 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -165,16 +177,12 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>SMA之ABS</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>均线</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>年化收益率</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>RSV</t>
@@ -193,23 +201,11 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>均线</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>成交量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回收资金</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -899,7 +895,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1211,6 +1207,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1220,7 +1219,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1531,6 +1530,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1574,7 +1576,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1886,6 +1888,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1895,7 +1900,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2206,6 +2211,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2249,7 +2257,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2561,6 +2569,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2570,7 +2581,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2881,6 +2892,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2903,11 +2917,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="505464704"/>
-        <c:axId val="505471744"/>
+        <c:axId val="621331200"/>
+        <c:axId val="621333504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="505464704"/>
+        <c:axId val="621331200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2950,14 +2964,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="505471744"/>
+        <c:crossAx val="621333504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="505471744"/>
+        <c:axId val="621333504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3006,7 +3020,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="505464704"/>
+        <c:crossAx val="621331200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3220,7 +3234,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3532,6 +3546,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3541,7 +3558,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3852,6 +3869,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3895,7 +3915,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4207,6 +4227,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4216,7 +4239,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4527,6 +4550,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4570,7 +4596,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4882,6 +4908,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4891,7 +4920,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5202,6 +5231,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5224,11 +5256,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="506795520"/>
-        <c:axId val="506797056"/>
+        <c:axId val="621570688"/>
+        <c:axId val="621572864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="506795520"/>
+        <c:axId val="621570688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5271,14 +5303,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506797056"/>
+        <c:crossAx val="621572864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="506797056"/>
+        <c:axId val="621572864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5327,7 +5359,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506795520"/>
+        <c:crossAx val="621570688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5541,7 +5573,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5853,6 +5885,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5862,7 +5897,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6173,6 +6208,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6216,7 +6254,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6528,6 +6566,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6537,7 +6578,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6848,6 +6889,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6891,7 +6935,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7203,6 +7247,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7212,7 +7259,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7523,6 +7570,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7545,11 +7595,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="517780224"/>
-        <c:axId val="517782528"/>
+        <c:axId val="688224128"/>
+        <c:axId val="691899776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="517780224"/>
+        <c:axId val="688224128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7592,14 +7642,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517782528"/>
+        <c:crossAx val="691899776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="517782528"/>
+        <c:axId val="691899776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7648,7 +7698,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517780224"/>
+        <c:crossAx val="688224128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7862,7 +7912,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8174,6 +8224,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8183,7 +8236,7 @@
               <c:f>'模型四 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8494,6 +8547,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8537,7 +8593,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8849,6 +8905,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8858,7 +8917,7 @@
               <c:f>'模型四 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9169,6 +9228,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9212,7 +9274,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9524,6 +9586,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9533,7 +9598,7 @@
               <c:f>'模型四 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9844,6 +9909,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -9866,11 +9934,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595792256"/>
-        <c:axId val="595793792"/>
+        <c:axId val="746396288"/>
+        <c:axId val="746402176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595792256"/>
+        <c:axId val="746396288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9913,14 +9981,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595793792"/>
+        <c:crossAx val="746402176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595793792"/>
+        <c:axId val="746402176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9969,7 +10037,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595792256"/>
+        <c:crossAx val="746396288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10183,7 +10251,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10495,6 +10563,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10504,7 +10575,7 @@
               <c:f>'模型四 (3)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10815,6 +10886,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -10858,7 +10932,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11170,6 +11244,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11179,7 +11256,7 @@
               <c:f>'模型四 (3)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11490,6 +11567,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11533,7 +11613,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11845,6 +11925,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11854,7 +11937,7 @@
               <c:f>'模型四 (3)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12165,6 +12248,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12187,11 +12273,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595855232"/>
-        <c:axId val="595856768"/>
+        <c:axId val="746632704"/>
+        <c:axId val="746634240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595855232"/>
+        <c:axId val="746632704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12234,14 +12320,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595856768"/>
+        <c:crossAx val="746634240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595856768"/>
+        <c:axId val="746634240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12290,7 +12376,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595855232"/>
+        <c:crossAx val="746632704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12504,7 +12590,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12816,6 +12902,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12825,7 +12914,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13136,6 +13225,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13179,7 +13271,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13491,6 +13583,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13500,7 +13595,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13811,6 +13906,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -13854,7 +13952,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14166,6 +14264,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14175,7 +14276,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14486,6 +14587,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14508,11 +14612,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="596109184"/>
-        <c:axId val="596110720"/>
+        <c:axId val="747124608"/>
+        <c:axId val="747126144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="596109184"/>
+        <c:axId val="747124608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14555,14 +14659,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596110720"/>
+        <c:crossAx val="747126144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="596110720"/>
+        <c:axId val="747126144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14611,7 +14715,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596109184"/>
+        <c:crossAx val="747124608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14825,7 +14929,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15137,6 +15241,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15146,7 +15253,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15457,6 +15564,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15500,7 +15610,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15812,6 +15922,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15821,7 +15934,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16132,6 +16245,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16175,7 +16291,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16487,6 +16603,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16496,7 +16615,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16807,6 +16926,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -16829,11 +16951,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="600802048"/>
-        <c:axId val="601266816"/>
+        <c:axId val="620981248"/>
+        <c:axId val="621679360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="600802048"/>
+        <c:axId val="620981248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16876,14 +16998,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601266816"/>
+        <c:crossAx val="621679360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="601266816"/>
+        <c:axId val="621679360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16932,7 +17054,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="600802048"/>
+        <c:crossAx val="620981248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17146,7 +17268,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17458,6 +17580,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17467,7 +17592,7 @@
               <c:f>'模型四 (3)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17778,6 +17903,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -17821,7 +17949,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18133,6 +18261,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18142,7 +18273,7 @@
               <c:f>'模型四 (3)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18453,6 +18584,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18496,7 +18630,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18808,6 +18942,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18817,7 +18954,7 @@
               <c:f>'模型四 (3)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19128,6 +19265,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="103">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19150,11 +19290,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="505785728"/>
-        <c:axId val="505787520"/>
+        <c:axId val="624902528"/>
+        <c:axId val="624904064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="505785728"/>
+        <c:axId val="624902528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19197,14 +19337,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="505787520"/>
+        <c:crossAx val="624904064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="505787520"/>
+        <c:axId val="624904064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19253,7 +19393,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="505785728"/>
+        <c:crossAx val="624902528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19361,7 +19501,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19404,7 +19544,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19447,7 +19587,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19490,7 +19630,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19533,7 +19673,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19576,7 +19716,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19619,7 +19759,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19662,7 +19802,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19975,7 +20115,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24413,6 +24553,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J108" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24431,7 +24606,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24469,10 +24644,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -24499,16 +24674,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -24533,7 +24708,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -30122,6 +30297,53 @@
         <v>63.365781700810651</v>
       </c>
       <c r="O107" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J108" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -30143,7 +30365,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30178,13 +30400,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -30211,19 +30433,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -36107,6 +36329,56 @@
         <v>64.562273357270726</v>
       </c>
       <c r="P107" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I108" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J108" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K108" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -36128,7 +36400,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36177,10 +36449,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -36204,7 +36476,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -41202,6 +41474,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M107" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K108" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L108" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M108" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>
@@ -41223,7 +41536,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41258,13 +41571,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -41365,7 +41678,7 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>12</v>
@@ -45658,6 +45971,41 @@
         <v>105.19592685297673</v>
       </c>
       <c r="K107" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I108" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J108" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K108" s="21">
         <v>260.7091440429981</v>
       </c>
     </row>
@@ -45679,7 +46027,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -45747,16 +46095,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -45863,7 +46211,7 @@
         <v>17</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -51370,6 +51718,53 @@
         <v>63.365781700810651</v>
       </c>
       <c r="O107" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="21">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I108" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J108" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K108" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L108" s="26">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="M108" s="27">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N108" s="27">
+        <v>67.765986815617211</v>
+      </c>
+      <c r="O108" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -51391,7 +51786,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51429,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -51459,19 +51854,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -57354,6 +57749,56 @@
         <v>64.562273357270726</v>
       </c>
       <c r="P107" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="21">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I108" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J108" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K108" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L108" s="26">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="M108" s="27">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="N108" s="27">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="O108" s="27">
+        <v>67.813131608977557</v>
+      </c>
+      <c r="P108" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -57375,7 +57820,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57418,16 +57863,16 @@
         <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -57451,7 +57896,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -57481,7 +57926,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -62449,6 +62894,47 @@
         <v>49.642090797890162</v>
       </c>
       <c r="M107" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="12.75">
+      <c r="A108" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B108" s="25">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.2814005657616347</v>
+      </c>
+      <c r="D108" s="20">
+        <v>1994182</v>
+      </c>
+      <c r="E108" s="20">
+        <v>1884119.8412663853</v>
+      </c>
+      <c r="F108" s="21">
+        <v>0</v>
+      </c>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22">
+        <v>0</v>
+      </c>
+      <c r="J108" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K108" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L108" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M108" s="21">
         <v>125.02031660046136</v>
       </c>
     </row>

--- a/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="39">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -153,6 +153,14 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -170,10 +178,6 @@
   </si>
   <si>
     <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -903,7 +907,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1221,6 +1225,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1230,7 +1237,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1547,6 +1554,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1590,7 +1600,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1908,6 +1918,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1917,7 +1930,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2234,6 +2247,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2277,7 +2293,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2595,6 +2611,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2604,7 +2623,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2921,6 +2940,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2943,11 +2965,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581600000"/>
-        <c:axId val="581601536"/>
+        <c:axId val="496200704"/>
+        <c:axId val="496210688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581600000"/>
+        <c:axId val="496200704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2990,14 +3012,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581601536"/>
+        <c:crossAx val="496210688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581601536"/>
+        <c:axId val="496210688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3046,7 +3068,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581600000"/>
+        <c:crossAx val="496200704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3260,7 +3282,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3578,6 +3600,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3587,7 +3612,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3904,6 +3929,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3947,7 +3975,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4265,6 +4293,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4274,7 +4305,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4591,6 +4622,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4634,7 +4668,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4952,6 +4986,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4961,7 +4998,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5278,6 +5315,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5300,11 +5340,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="587047680"/>
-        <c:axId val="587049216"/>
+        <c:axId val="496827776"/>
+        <c:axId val="497297280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="587047680"/>
+        <c:axId val="496827776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5347,14 +5387,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="587049216"/>
+        <c:crossAx val="497297280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="587049216"/>
+        <c:axId val="497297280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5403,7 +5443,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="587047680"/>
+        <c:crossAx val="496827776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5617,7 +5657,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5935,6 +5975,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5944,7 +5987,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6261,6 +6304,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6304,7 +6350,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6622,6 +6668,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6631,7 +6680,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6948,6 +6997,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -6991,7 +7043,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7309,6 +7361,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7318,7 +7373,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7635,6 +7690,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7657,11 +7715,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="613202944"/>
-        <c:axId val="613209216"/>
+        <c:axId val="508577280"/>
+        <c:axId val="508579200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="613202944"/>
+        <c:axId val="508577280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7704,14 +7762,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613209216"/>
+        <c:crossAx val="508579200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="613209216"/>
+        <c:axId val="508579200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7760,7 +7818,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613202944"/>
+        <c:crossAx val="508577280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7974,7 +8032,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8292,6 +8350,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8301,7 +8362,7 @@
               <c:f>'模型四 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8618,6 +8679,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8661,7 +8725,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8979,6 +9043,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8988,7 +9055,7 @@
               <c:f>'模型四 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9305,6 +9372,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9348,7 +9418,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9666,6 +9736,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9675,7 +9748,7 @@
               <c:f>'模型四 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9992,6 +10065,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10014,11 +10090,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="635684736"/>
-        <c:axId val="635686272"/>
+        <c:axId val="609983488"/>
+        <c:axId val="609997568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="635684736"/>
+        <c:axId val="609983488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10061,14 +10137,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="635686272"/>
+        <c:crossAx val="609997568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="635686272"/>
+        <c:axId val="609997568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10117,7 +10193,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="635684736"/>
+        <c:crossAx val="609983488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10331,7 +10407,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10649,6 +10725,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10658,7 +10737,7 @@
               <c:f>'模型四 (3)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10975,6 +11054,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11018,7 +11100,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11336,6 +11418,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11345,7 +11430,7 @@
               <c:f>'模型四 (3)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11662,6 +11747,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11705,7 +11793,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12023,6 +12111,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12032,7 +12123,7 @@
               <c:f>'模型四 (3)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12349,6 +12440,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12371,11 +12465,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="661227392"/>
-        <c:axId val="661242240"/>
+        <c:axId val="614071680"/>
+        <c:axId val="614073856"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="661227392"/>
+        <c:axId val="614071680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12418,14 +12512,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="661242240"/>
+        <c:crossAx val="614073856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="661242240"/>
+        <c:axId val="614073856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12474,7 +12568,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="661227392"/>
+        <c:crossAx val="614071680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12688,7 +12782,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13006,6 +13100,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13015,7 +13112,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13332,6 +13429,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13375,7 +13475,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13693,6 +13793,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13702,7 +13805,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14019,6 +14122,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14062,7 +14168,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14380,6 +14486,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14389,7 +14498,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14706,6 +14815,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14728,11 +14840,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="661273984"/>
-        <c:axId val="661492864"/>
+        <c:axId val="614108544"/>
+        <c:axId val="614147968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="661273984"/>
+        <c:axId val="614108544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14775,14 +14887,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="661492864"/>
+        <c:crossAx val="614147968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="661492864"/>
+        <c:axId val="614147968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14831,7 +14943,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="661273984"/>
+        <c:crossAx val="614108544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15045,7 +15157,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15363,6 +15475,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15372,7 +15487,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15689,6 +15804,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15732,7 +15850,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16050,6 +16168,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16059,7 +16180,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16376,6 +16497,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16419,7 +16543,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16737,6 +16861,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16746,7 +16873,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17063,6 +17190,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17085,11 +17215,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="661829504"/>
-        <c:axId val="662114688"/>
+        <c:axId val="614244736"/>
+        <c:axId val="614246656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="661829504"/>
+        <c:axId val="614244736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17132,14 +17262,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662114688"/>
+        <c:crossAx val="614246656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662114688"/>
+        <c:axId val="614246656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17188,7 +17318,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="661829504"/>
+        <c:crossAx val="614244736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17402,7 +17532,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17720,6 +17850,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17729,7 +17862,7 @@
               <c:f>'模型四 (3)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18046,6 +18179,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18089,7 +18225,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18407,6 +18543,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18416,7 +18555,7 @@
               <c:f>'模型四 (3)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18733,6 +18872,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -18776,7 +18918,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19094,6 +19236,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19103,7 +19248,7 @@
               <c:f>'模型四 (3)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19420,6 +19565,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19442,11 +19590,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="580894720"/>
-        <c:axId val="580896256"/>
+        <c:axId val="489749120"/>
+        <c:axId val="495083904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="580894720"/>
+        <c:axId val="489749120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19489,14 +19637,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580896256"/>
+        <c:crossAx val="495083904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="580896256"/>
+        <c:axId val="495083904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19545,7 +19693,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580894720"/>
+        <c:crossAx val="489749120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20267,7 +20415,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24775,6 +24923,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J110" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -24793,7 +24976,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24831,7 +25014,7 @@
         <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -24861,16 +25044,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -30578,6 +30761,53 @@
         <v>73.035028220618088</v>
       </c>
       <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J110" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -30599,7 +30829,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30634,13 +30864,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -30667,19 +30897,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -36663,6 +36893,56 @@
         <v>78.982013449904031</v>
       </c>
       <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J110" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -36684,7 +36964,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36733,10 +37013,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -36748,10 +37028,10 @@
         <v>5</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K1" s="30" t="s">
         <v>8</v>
@@ -41840,6 +42120,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M109" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K110" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L110" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M110" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>
@@ -41861,7 +42182,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41952,7 +42273,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -46366,6 +46687,41 @@
         <v>105.19592685297673</v>
       </c>
       <c r="K109" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I110" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J110" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K110" s="21">
         <v>260.7091440429981</v>
       </c>
     </row>
@@ -46387,7 +46743,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46455,16 +46811,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -52172,6 +52528,53 @@
         <v>73.035028220618088</v>
       </c>
       <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="21">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I110" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J110" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K110" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -52193,7 +52596,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -52228,10 +52631,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -52261,19 +52664,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -58256,6 +58659,56 @@
         <v>78.982013449904031</v>
       </c>
       <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I110" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J110" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K110" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -58277,7 +58730,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -58323,13 +58776,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -63436,6 +63889,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K110" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L110" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M110" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -145,23 +145,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>人工智能产业LOF</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
+    <t>均线</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -181,10 +169,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>RSV</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -201,23 +185,27 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市值</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>累计投入资金</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +895,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1231,6 +1219,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1240,7 +1231,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1563,6 +1554,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1606,7 +1600,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1930,6 +1924,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1939,7 +1936,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2262,6 +2259,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2305,7 +2305,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2629,6 +2629,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2638,7 +2641,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2961,6 +2964,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2983,11 +2989,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440885632"/>
-        <c:axId val="440887168"/>
+        <c:axId val="527319808"/>
+        <c:axId val="527321344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440885632"/>
+        <c:axId val="527319808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3030,14 +3036,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440887168"/>
+        <c:crossAx val="527321344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440887168"/>
+        <c:axId val="527321344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3086,7 +3092,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440885632"/>
+        <c:crossAx val="527319808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3300,7 +3306,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3624,6 +3630,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3633,7 +3642,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3956,6 +3965,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3999,7 +4011,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4323,6 +4335,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4332,7 +4347,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4655,6 +4670,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4698,7 +4716,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5022,6 +5040,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5031,7 +5052,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5354,6 +5375,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5376,11 +5400,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="441169024"/>
-        <c:axId val="441170560"/>
+        <c:axId val="565408512"/>
+        <c:axId val="565410048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="441169024"/>
+        <c:axId val="565408512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5423,14 +5447,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="441170560"/>
+        <c:crossAx val="565410048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="441170560"/>
+        <c:axId val="565410048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5479,7 +5503,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="441169024"/>
+        <c:crossAx val="565408512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5693,7 +5717,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6017,6 +6041,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6026,7 +6053,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6349,6 +6376,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6392,7 +6422,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6716,6 +6746,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6725,7 +6758,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7048,6 +7081,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7091,7 +7127,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7415,6 +7451,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7424,7 +7463,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7747,6 +7786,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7769,11 +7811,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="493529728"/>
-        <c:axId val="493716224"/>
+        <c:axId val="598616320"/>
+        <c:axId val="598631168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="493529728"/>
+        <c:axId val="598616320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7816,14 +7858,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493716224"/>
+        <c:crossAx val="598631168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493716224"/>
+        <c:axId val="598631168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7872,7 +7914,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493529728"/>
+        <c:crossAx val="598616320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8086,7 +8128,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8410,6 +8452,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8419,7 +8464,7 @@
               <c:f>'模型四 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8742,6 +8787,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8785,7 +8833,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9109,6 +9157,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9118,7 +9169,7 @@
               <c:f>'模型四 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9441,6 +9492,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9484,7 +9538,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9808,6 +9862,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9817,7 +9874,7 @@
               <c:f>'模型四 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10140,6 +10197,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10162,11 +10222,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494302336"/>
-        <c:axId val="494303872"/>
+        <c:axId val="598645376"/>
+        <c:axId val="598651264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494302336"/>
+        <c:axId val="598645376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10209,14 +10269,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494303872"/>
+        <c:crossAx val="598651264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494303872"/>
+        <c:axId val="598651264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10265,7 +10325,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494302336"/>
+        <c:crossAx val="598645376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10479,7 +10539,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10803,6 +10863,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10812,7 +10875,7 @@
               <c:f>'模型四 (3)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11135,6 +11198,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11178,7 +11244,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11502,6 +11568,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11511,7 +11580,7 @@
               <c:f>'模型四 (3)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11834,6 +11903,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11877,7 +11949,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12201,6 +12273,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12210,7 +12285,7 @@
               <c:f>'模型四 (3)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12533,6 +12608,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12555,11 +12633,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494342528"/>
-        <c:axId val="500363648"/>
+        <c:axId val="598769664"/>
+        <c:axId val="598771584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494342528"/>
+        <c:axId val="598769664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12602,14 +12680,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500363648"/>
+        <c:crossAx val="598771584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="500363648"/>
+        <c:axId val="598771584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12658,7 +12736,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494342528"/>
+        <c:crossAx val="598769664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12872,7 +12950,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13196,6 +13274,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13205,7 +13286,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13528,6 +13609,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13571,7 +13655,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13895,6 +13979,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13904,7 +13991,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14227,6 +14314,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14270,7 +14360,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14594,6 +14684,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14603,7 +14696,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14926,6 +15019,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14948,11 +15044,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438264960"/>
-        <c:axId val="438266496"/>
+        <c:axId val="512018304"/>
+        <c:axId val="512019840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438264960"/>
+        <c:axId val="512018304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14995,14 +15091,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438266496"/>
+        <c:crossAx val="512019840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438266496"/>
+        <c:axId val="512019840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15051,7 +15147,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438264960"/>
+        <c:crossAx val="512018304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15265,7 +15361,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15589,6 +15685,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15598,7 +15697,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15921,6 +16020,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15964,7 +16066,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16288,6 +16390,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16297,7 +16402,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16620,6 +16725,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16663,7 +16771,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16987,6 +17095,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16996,7 +17107,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17319,6 +17430,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17341,11 +17455,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="439933184"/>
-        <c:axId val="440336384"/>
+        <c:axId val="522853376"/>
+        <c:axId val="522855168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="439933184"/>
+        <c:axId val="522853376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17388,14 +17502,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440336384"/>
+        <c:crossAx val="522855168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440336384"/>
+        <c:axId val="522855168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17444,7 +17558,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="439933184"/>
+        <c:crossAx val="522853376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17658,7 +17772,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17982,6 +18096,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17991,7 +18108,7 @@
               <c:f>'模型四 (3)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18314,6 +18431,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18357,7 +18477,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18681,6 +18801,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18690,7 +18813,7 @@
               <c:f>'模型四 (3)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19013,6 +19136,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19056,7 +19182,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19380,6 +19506,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19389,7 +19518,7 @@
               <c:f>'模型四 (3)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19712,6 +19841,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19734,11 +19866,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440507776"/>
-        <c:axId val="440566912"/>
+        <c:axId val="527159680"/>
+        <c:axId val="527161216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440507776"/>
+        <c:axId val="527159680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19781,14 +19913,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440566912"/>
+        <c:crossAx val="527161216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440566912"/>
+        <c:axId val="527161216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19837,7 +19969,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440507776"/>
+        <c:crossAx val="527159680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20559,7 +20691,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25137,6 +25269,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J112" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25155,7 +25322,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25190,13 +25357,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -25223,16 +25390,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -31034,6 +31201,53 @@
         <v>53.107937195450262</v>
       </c>
       <c r="O111" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J112" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L112" s="26">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="M112" s="27">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N112" s="27">
+        <v>69.387397039635189</v>
+      </c>
+      <c r="O112" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -31055,7 +31269,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31090,10 +31304,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -31123,19 +31337,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -31160,7 +31374,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -37219,6 +37433,56 @@
         <v>64.583952119551526</v>
       </c>
       <c r="P111" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I112" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J112" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K112" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L112" s="26">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="M112" s="27">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="N112" s="27">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="O112" s="27">
+        <v>87.102862652376814</v>
+      </c>
+      <c r="P112" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -37240,7 +37504,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37280,13 +37544,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>34</v>
@@ -42478,6 +42742,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M111" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="20">
+        <v>1395013</v>
+      </c>
+      <c r="E112" s="20">
+        <v>1856713.9160601357</v>
+      </c>
+      <c r="F112" s="21">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>0</v>
+      </c>
+      <c r="I112" s="22">
+        <v>0</v>
+      </c>
+      <c r="J112" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K112" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L112" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M112" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>
@@ -42499,7 +42804,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -42534,10 +42839,10 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -42590,7 +42895,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -47074,6 +47379,41 @@
         <v>105.19592685297673</v>
       </c>
       <c r="K111" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I112" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J112" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K112" s="21">
         <v>260.7091440429981</v>
       </c>
     </row>
@@ -47095,7 +47435,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -47130,13 +47470,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>29</v>
-      </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -47163,16 +47503,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -52974,6 +53314,53 @@
         <v>53.107937195450262</v>
       </c>
       <c r="O111" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="21">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I112" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J112" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K112" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L112" s="26">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="M112" s="27">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N112" s="27">
+        <v>69.387397039635189</v>
+      </c>
+      <c r="O112" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -52995,7 +53382,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -53030,13 +53417,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -53063,19 +53450,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -59158,6 +59545,56 @@
         <v>64.583952119551526</v>
       </c>
       <c r="P111" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I112" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J112" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K112" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L112" s="26">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="M112" s="27">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="N112" s="27">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="O112" s="27">
+        <v>87.102862652376814</v>
+      </c>
+      <c r="P112" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -59179,7 +59616,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -59219,13 +59656,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>34</v>
@@ -59243,10 +59680,10 @@
         <v>5</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K1" s="30" t="s">
         <v>8</v>
@@ -59285,7 +59722,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -64417,6 +64854,47 @@
         <v>49.642090797890162</v>
       </c>
       <c r="M111" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="12.75">
+      <c r="A112" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B112" s="25">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.3244243374307696</v>
+      </c>
+      <c r="D112" s="20">
+        <v>1395013</v>
+      </c>
+      <c r="E112" s="20">
+        <v>1856713.9160601357</v>
+      </c>
+      <c r="F112" s="21">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>0</v>
+      </c>
+      <c r="I112" s="22">
+        <v>0</v>
+      </c>
+      <c r="J112" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K112" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L112" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M112" s="21">
         <v>125.02031660046136</v>
       </c>
     </row>

--- a/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="35">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -145,11 +145,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>人工智能产业LOF</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>均线</t>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -169,6 +177,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>RSV</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -182,22 +194,6 @@
   </si>
   <si>
     <t>J</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>均线</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>均线</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -895,7 +891,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1222,6 +1218,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1231,7 +1230,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1557,6 +1556,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1600,7 +1602,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1927,6 +1929,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1936,7 +1941,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2262,6 +2267,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2305,7 +2313,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2632,6 +2640,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2641,7 +2652,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2967,6 +2978,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2989,11 +3003,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527319808"/>
-        <c:axId val="527321344"/>
+        <c:axId val="501087232"/>
+        <c:axId val="504140544"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527319808"/>
+        <c:axId val="501087232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3036,14 +3050,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527321344"/>
+        <c:crossAx val="504140544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527321344"/>
+        <c:axId val="504140544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3092,7 +3106,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527319808"/>
+        <c:crossAx val="501087232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3306,7 +3320,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3633,6 +3647,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3642,7 +3659,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3968,6 +3985,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -4011,7 +4031,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4338,6 +4358,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4347,7 +4370,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4673,6 +4696,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4716,7 +4742,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5043,6 +5069,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5052,7 +5081,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5378,6 +5407,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5400,11 +5432,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="565408512"/>
-        <c:axId val="565410048"/>
+        <c:axId val="505314304"/>
+        <c:axId val="511238912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="565408512"/>
+        <c:axId val="505314304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5447,14 +5479,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565410048"/>
+        <c:crossAx val="511238912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="565410048"/>
+        <c:axId val="511238912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5503,7 +5535,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565408512"/>
+        <c:crossAx val="505314304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5717,7 +5749,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6044,6 +6076,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6053,7 +6088,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6379,6 +6414,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6422,7 +6460,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6749,6 +6787,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6758,7 +6799,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7084,6 +7125,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7127,7 +7171,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7454,6 +7498,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7463,7 +7510,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7789,6 +7836,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7811,11 +7861,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="598616320"/>
-        <c:axId val="598631168"/>
+        <c:axId val="625039232"/>
+        <c:axId val="625090560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598616320"/>
+        <c:axId val="625039232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7858,14 +7908,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598631168"/>
+        <c:crossAx val="625090560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598631168"/>
+        <c:axId val="625090560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7914,7 +7964,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598616320"/>
+        <c:crossAx val="625039232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8128,7 +8178,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8455,6 +8505,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8464,7 +8517,7 @@
               <c:f>'模型四 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8790,6 +8843,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8833,7 +8889,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9160,6 +9216,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9169,7 +9228,7 @@
               <c:f>'模型四 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9495,6 +9554,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9538,7 +9600,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9865,6 +9927,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9874,7 +9939,7 @@
               <c:f>'模型四 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10200,6 +10265,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10222,11 +10290,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="598645376"/>
-        <c:axId val="598651264"/>
+        <c:axId val="625137920"/>
+        <c:axId val="625140096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598645376"/>
+        <c:axId val="625137920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10269,14 +10337,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598651264"/>
+        <c:crossAx val="625140096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598651264"/>
+        <c:axId val="625140096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10325,7 +10393,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598645376"/>
+        <c:crossAx val="625137920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10539,7 +10607,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10866,6 +10934,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10875,7 +10946,7 @@
               <c:f>'模型四 (3)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11201,6 +11272,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11244,7 +11318,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11571,6 +11645,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11580,7 +11657,7 @@
               <c:f>'模型四 (3)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11906,6 +11983,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11949,7 +12029,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12276,6 +12356,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12285,7 +12368,7 @@
               <c:f>'模型四 (3)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12611,6 +12694,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12633,11 +12719,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="598769664"/>
-        <c:axId val="598771584"/>
+        <c:axId val="628857088"/>
+        <c:axId val="628871168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598769664"/>
+        <c:axId val="628857088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12680,14 +12766,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598771584"/>
+        <c:crossAx val="628871168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598771584"/>
+        <c:axId val="628871168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12736,7 +12822,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598769664"/>
+        <c:crossAx val="628857088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12950,7 +13036,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13277,6 +13363,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13286,7 +13375,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13612,6 +13701,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13655,7 +13747,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13982,6 +14074,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13991,7 +14086,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14317,6 +14412,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14360,7 +14458,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14687,6 +14785,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14696,7 +14797,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15022,6 +15123,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -15044,11 +15148,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="512018304"/>
-        <c:axId val="512019840"/>
+        <c:axId val="654067968"/>
+        <c:axId val="654192640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="512018304"/>
+        <c:axId val="654067968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15091,14 +15195,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="512019840"/>
+        <c:crossAx val="654192640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="512019840"/>
+        <c:axId val="654192640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15147,7 +15251,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="512018304"/>
+        <c:crossAx val="654067968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15361,7 +15465,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15688,6 +15792,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15697,7 +15804,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16023,6 +16130,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -16066,7 +16176,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16393,6 +16503,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16402,7 +16515,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16728,6 +16841,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16771,7 +16887,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17098,6 +17214,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17107,7 +17226,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17433,6 +17552,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17455,11 +17577,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522853376"/>
-        <c:axId val="522855168"/>
+        <c:axId val="467616512"/>
+        <c:axId val="467618048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522853376"/>
+        <c:axId val="467616512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17502,14 +17624,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522855168"/>
+        <c:crossAx val="467618048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522855168"/>
+        <c:axId val="467618048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17558,7 +17680,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522853376"/>
+        <c:crossAx val="467616512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17772,7 +17894,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18099,6 +18221,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18108,7 +18233,7 @@
               <c:f>'模型四 (3)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18434,6 +18559,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18477,7 +18605,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18804,6 +18932,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18813,7 +18944,7 @@
               <c:f>'模型四 (3)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19139,6 +19270,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19182,7 +19316,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19509,6 +19643,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19518,7 +19655,7 @@
               <c:f>'模型四 (3)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19844,6 +19981,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19866,11 +20006,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527159680"/>
-        <c:axId val="527161216"/>
+        <c:axId val="497088384"/>
+        <c:axId val="497089920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527159680"/>
+        <c:axId val="497088384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19913,14 +20053,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527161216"/>
+        <c:crossAx val="497089920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527161216"/>
+        <c:axId val="497089920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19969,7 +20109,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527159680"/>
+        <c:crossAx val="497088384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20691,7 +20831,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25304,6 +25444,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J113" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25322,7 +25497,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25357,13 +25532,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -25390,16 +25565,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -25485,7 +25660,7 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -31248,6 +31423,53 @@
         <v>69.387397039635189</v>
       </c>
       <c r="O112" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J113" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L113" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M113" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N113" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O113" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -31269,7 +31491,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31304,13 +31526,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -31337,19 +31559,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -31374,7 +31596,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -31439,7 +31661,7 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -37483,6 +37705,56 @@
         <v>87.102862652376814</v>
       </c>
       <c r="P112" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I113" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J113" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K113" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L113" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M113" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N113" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O113" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P113" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -37504,7 +37776,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37544,19 +37816,19 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -37667,7 +37939,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -42783,6 +43055,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M112" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="20">
+        <v>1204034</v>
+      </c>
+      <c r="E113" s="20">
+        <v>1851506.4082384438</v>
+      </c>
+      <c r="F113" s="21">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>0</v>
+      </c>
+      <c r="I113" s="22">
+        <v>0</v>
+      </c>
+      <c r="J113" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K113" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L113" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M113" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>
@@ -42804,7 +43117,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -42839,10 +43152,10 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -42946,7 +43259,7 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>12</v>
@@ -47414,6 +47727,41 @@
         <v>105.19592685297673</v>
       </c>
       <c r="K112" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I113" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J113" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K113" s="21">
         <v>260.7091440429981</v>
       </c>
     </row>
@@ -47435,7 +47783,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -47470,13 +47818,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -47503,16 +47851,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -47598,7 +47946,7 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -53361,6 +53709,53 @@
         <v>69.387397039635189</v>
       </c>
       <c r="O112" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="21">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I113" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J113" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K113" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L113" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M113" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N113" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O113" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -53382,7 +53777,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -53417,13 +53812,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -53450,19 +53845,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -53552,7 +53947,7 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -59595,6 +59990,56 @@
         <v>87.102862652376814</v>
       </c>
       <c r="P112" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I113" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J113" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K113" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L113" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M113" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N113" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O113" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P113" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -59616,7 +60061,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -59656,19 +60101,19 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -59779,7 +60224,7 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>12</v>
@@ -64895,6 +65340,47 @@
         <v>49.642090797890162</v>
       </c>
       <c r="M112" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="12.75">
+      <c r="A113" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B113" s="25">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.3386396909952163</v>
+      </c>
+      <c r="D113" s="20">
+        <v>1204034</v>
+      </c>
+      <c r="E113" s="20">
+        <v>1851506.4082384438</v>
+      </c>
+      <c r="F113" s="21">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>0</v>
+      </c>
+      <c r="I113" s="22">
+        <v>0</v>
+      </c>
+      <c r="J113" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K113" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L113" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M113" s="21">
         <v>125.02031660046136</v>
       </c>
     </row>
